--- a/src/cubes/data/materials/materials.xlsx
+++ b/src/cubes/data/materials/materials.xlsx
@@ -363,7 +363,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -392,15 +392,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -413,23 +417,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF3D3D3D"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -439,7 +426,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.51171875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="20.83"/>
@@ -705,11 +692,11 @@
         <f aca="false">I6</f>
         <v>0.7</v>
       </c>
-      <c r="J7" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="6" t="b">
+      <c r="J7" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -744,11 +731,11 @@
         <f aca="false">I7</f>
         <v>0.7</v>
       </c>
-      <c r="J8" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="b">
+      <c r="J8" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -783,11 +770,11 @@
         <f aca="false">I8</f>
         <v>0.7</v>
       </c>
-      <c r="J9" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="b">
+      <c r="J9" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -822,11 +809,11 @@
         <f aca="false">I9</f>
         <v>0.7</v>
       </c>
-      <c r="J10" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="b">
+      <c r="J10" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -861,11 +848,11 @@
         <f aca="false">I10</f>
         <v>0.7</v>
       </c>
-      <c r="J11" s="6" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="6" t="b">
+      <c r="J11" s="7" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1559,11 +1546,11 @@
         <f aca="false">I28</f>
         <v>0.7</v>
       </c>
-      <c r="J29" s="0" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="0" t="b">
+      <c r="J29" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1598,11 +1585,11 @@
         <f aca="false">I29</f>
         <v>0.7</v>
       </c>
-      <c r="J30" s="0" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="0" t="b">
+      <c r="J30" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1637,11 +1624,11 @@
         <f aca="false">I30</f>
         <v>0.7</v>
       </c>
-      <c r="J31" s="0" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="0" t="b">
+      <c r="J31" s="6" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1665,11 +1652,11 @@
       <c r="I32" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J32" s="0" t="b">
+      <c r="J32" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K32" s="0" t="b">
+      <c r="K32" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -1759,7 +1746,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="4"/>
@@ -1790,7 +1777,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B37" s="4" t="n">
@@ -1825,7 +1812,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B38" s="4" t="n">
@@ -1860,7 +1847,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B39" s="4" t="n">
@@ -1895,7 +1882,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="4"/>
@@ -1926,7 +1913,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B41" s="4" t="n">
@@ -1961,7 +1948,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B42" s="4" t="n">
@@ -1996,7 +1983,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="4"/>
@@ -2015,7 +2002,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B44" s="4" t="n">
@@ -2040,7 +2027,7 @@
       <c r="I44" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J44" s="0" t="b">
+      <c r="J44" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2050,7 +2037,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B45" s="4"/>
@@ -2069,7 +2056,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B46" s="4" t="n">
@@ -2094,7 +2081,7 @@
       <c r="I46" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J46" s="0" t="b">
+      <c r="J46" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2104,7 +2091,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B47" s="4" t="n">
@@ -2129,7 +2116,7 @@
       <c r="I47" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J47" s="0" t="b">
+      <c r="J47" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2139,7 +2126,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B48" s="4" t="n">
@@ -2164,7 +2151,7 @@
       <c r="I48" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J48" s="0" t="b">
+      <c r="J48" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2174,7 +2161,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="4" t="n">
@@ -2192,7 +2179,7 @@
       <c r="I49" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J49" s="0" t="b">
+      <c r="J49" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2202,7 +2189,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C50" s="4" t="n">
@@ -2220,17 +2207,15 @@
       <c r="I50" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J50" s="0" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="0" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="J50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C51" s="4" t="n">
@@ -2248,744 +2233,744 @@
       <c r="I51" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="J51" s="8" t="n">
+      <c r="J51" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="8" t="n">
+      <c r="K51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B52" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7" t="n">
+      <c r="C52" s="8"/>
+      <c r="D52" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G52" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J52" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K52" s="7" t="b">
+      <c r="G52" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J52" s="9" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K52" s="9" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7" t="n">
+      <c r="C53" s="8"/>
+      <c r="D53" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E53" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G53" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J53" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="7" t="b">
+      <c r="G53" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J53" s="9" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="9" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7" t="n">
+      <c r="C54" s="8"/>
+      <c r="D54" s="8" t="n">
         <v>2300</v>
       </c>
-      <c r="E54" s="7" t="n">
+      <c r="E54" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G54" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J54" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="7" t="b">
+      <c r="G54" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J54" s="9" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7" t="n">
+      <c r="B55" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8" t="n">
         <v>1400</v>
       </c>
-      <c r="E55" s="7" t="n">
+      <c r="E55" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G55" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H55" s="7" t="n">
+      <c r="G55" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H55" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="I55" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J55" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K55" s="7" t="b">
+      <c r="I55" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J55" s="9" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K55" s="9" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7" t="n">
+      <c r="C56" s="8"/>
+      <c r="D56" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E56" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G56" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H56" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I56" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J56" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="7" t="b">
+      <c r="G56" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J56" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7" t="n">
+      <c r="C57" s="8"/>
+      <c r="D57" s="8" t="n">
         <v>2300</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" s="8" t="n">
         <v>1100</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G57" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H57" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J57" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="7" t="b">
+      <c r="G57" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J57" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7" t="n">
+      <c r="C58" s="8"/>
+      <c r="D58" s="8" t="n">
         <v>2300</v>
       </c>
-      <c r="E58" s="7" t="n">
+      <c r="E58" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G58" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J58" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="7" t="b">
+      <c r="G58" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J58" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7" t="n">
+      <c r="C59" s="8"/>
+      <c r="D59" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E59" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G59" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H59" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J59" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="7" t="b">
+      <c r="G59" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J59" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="7" t="n">
+      <c r="B60" s="8" t="n">
         <v>1.4</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7" t="n">
+      <c r="C60" s="8"/>
+      <c r="D60" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E60" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G60" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H60" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I60" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J60" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="7" t="b">
+      <c r="G60" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J60" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B61" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7" t="n">
+      <c r="C61" s="8"/>
+      <c r="D61" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E61" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G61" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H61" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I61" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J61" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K61" s="7" t="b">
+      <c r="G61" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J61" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K61" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="8" t="n">
         <v>0.16</v>
       </c>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7" t="n">
+      <c r="C62" s="8"/>
+      <c r="D62" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="E62" s="7" t="n">
+      <c r="E62" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H62" s="7" t="n">
+      <c r="G62" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H62" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="I62" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="J62" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K62" s="7" t="b">
+      <c r="J62" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K62" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="8" t="n">
         <v>0.035</v>
       </c>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7" t="n">
+      <c r="C63" s="8"/>
+      <c r="D63" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H63" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I63" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J63" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="7" t="b">
+      <c r="G63" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J63" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7" t="n">
+      <c r="B64" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8" t="n">
         <v>1400</v>
       </c>
-      <c r="E64" s="7" t="n">
+      <c r="E64" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G64" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H64" s="7" t="n">
+      <c r="G64" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H64" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="I64" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J64" s="9" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="9" t="b">
+      <c r="I64" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J64" s="10" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="10" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7" t="n">
+      <c r="C65" s="8"/>
+      <c r="D65" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="H65" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="I65" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J65" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="7" t="b">
+      <c r="I65" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J65" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="B66" s="8" t="n">
         <v>1.13</v>
       </c>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7" t="n">
+      <c r="C66" s="8"/>
+      <c r="D66" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E66" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H66" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J66" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="7" t="b">
+      <c r="G66" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I66" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J66" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="8" t="n">
         <v>0.14</v>
       </c>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7" t="n">
+      <c r="C67" s="8"/>
+      <c r="D67" s="8" t="n">
         <v>650</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E67" s="8" t="n">
         <v>2300</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G67" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H67" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J67" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="7" t="b">
+      <c r="G67" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J67" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="B68" s="8" t="n">
         <v>0.05</v>
       </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7" t="n">
+      <c r="C68" s="8"/>
+      <c r="D68" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E68" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H68" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J68" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="7" t="b">
+      <c r="G68" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J68" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="7" t="n">
+      <c r="B69" s="8" t="n">
         <v>0.84</v>
       </c>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7" t="n">
+      <c r="C69" s="8"/>
+      <c r="D69" s="8" t="n">
         <v>1700</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H69" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J69" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="7" t="b">
+      <c r="G69" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J69" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B70" s="7" t="n">
+      <c r="B70" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7" t="n">
+      <c r="C70" s="8"/>
+      <c r="D70" s="8" t="n">
         <v>1300</v>
       </c>
-      <c r="E70" s="7" t="n">
+      <c r="E70" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G70" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H70" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I70" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J70" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="7" t="b">
+      <c r="G70" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J70" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K70" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B71" s="7" t="n">
+      <c r="B71" s="8" t="n">
         <v>0.71</v>
       </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7" t="n">
+      <c r="C71" s="8"/>
+      <c r="D71" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="8" t="n">
         <v>1380</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G71" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H71" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J71" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="7" t="b">
+      <c r="G71" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J71" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="7" t="n">
+      <c r="B72" s="8" t="n">
         <v>0.14</v>
       </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7" t="n">
+      <c r="C72" s="8"/>
+      <c r="D72" s="8" t="n">
         <v>650</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E72" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H72" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J72" s="7" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="7" t="b">
+      <c r="G72" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J72" s="8" t="b">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/src/cubes/data/materials/materials.xlsx
+++ b/src/cubes/data/materials/materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/elizabeth-homes/src/cubes/data/materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/CUBES/src/cubes/data/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFBE6E-E950-9A49-AF5C-57CFBE959AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9E57AC-A472-FD41-88AE-25F4B49D6A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="2300" windowWidth="26660" windowHeight="15800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="560" yWindow="-15760" windowWidth="26660" windowHeight="15800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
   <si>
     <t>Material</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>Joists_with_100mm_insulation_CODE</t>
+  </si>
+  <si>
+    <t>Floor_joists_with_120mm_insulation_CODE</t>
   </si>
 </sst>
 </file>
@@ -711,10 +714,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="22.6640625" customWidth="1"/>
@@ -3740,6 +3743,38 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="D89">
+        <v>71</v>
+      </c>
+      <c r="E89">
+        <v>170</v>
+      </c>
+      <c r="F89" t="s">
+        <v>47</v>
+      </c>
+      <c r="G89">
+        <v>0.9</v>
+      </c>
+      <c r="H89">
+        <v>0.7</v>
+      </c>
+      <c r="I89">
+        <v>0.7</v>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
